--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487160_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487160_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6501</v>
+        <v>0.897</v>
       </c>
       <c r="E2" t="n">
-        <v>0.312</v>
+        <v>0.3714</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3382</v>
+        <v>0.5256</v>
       </c>
       <c r="G2" t="n">
         <v>1.6483</v>
@@ -610,13 +610,13 @@
         <v>0.386</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0331</v>
+        <v>-0.7863</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3569</v>
+        <v>-0.2974</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6762</v>
+        <v>-0.4888</v>
       </c>
       <c r="V2" t="n">
         <v>0.614</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2267</v>
+        <v>0.8335</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7961</v>
+        <v>3.2155</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.5695</v>
+        <v>-2.3821</v>
       </c>
       <c r="G3" t="n">
         <v>1.6238</v>
@@ -688,13 +688,13 @@
         <v>1.158</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.3392</v>
+        <v>-1.7325</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.4132</v>
+        <v>-0.9938</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9261</v>
+        <v>-0.7387</v>
       </c>
       <c r="V3" t="n">
         <v>0.9421</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. CAMPBELL</t>
+          <t>H. BARREIRO ESCARCEGA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0231</v>
+        <v>-0.7884</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9681</v>
+        <v>-0.6826</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9912</v>
+        <v>-0.1058</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.389</v>
+        <v>-0.6516</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.6828</v>
+        <v>-0.1924</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7062</v>
+        <v>-0.4591</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4275</v>
+        <v>-0.5448</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0205</v>
+        <v>0.0414</v>
       </c>
       <c r="L4" t="n">
-        <v>0.407</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.8164</v>
+        <v>-0.1067</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.7033</v>
+        <v>-0.2338</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1132</v>
+        <v>0.1271</v>
       </c>
       <c r="P4" t="n">
         <v>0.386</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.158</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5441</v>
+        <v>0.386</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0377</v>
+        <v>-0.5228</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4707</v>
+        <v>-0.1378</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5671</v>
+        <v>-0.385</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9421</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. BARREIRO ESCARCEGA</t>
+          <t>S. CAMPBELL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1413</v>
+        <v>-1.5421</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9016999999999999</v>
+        <v>0.1451</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2396</v>
+        <v>-1.6872</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6516</v>
+        <v>-2.389</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1924</v>
+        <v>-1.6828</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4591</v>
+        <v>-0.7062</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5448</v>
+        <v>0.4275</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0414</v>
+        <v>0.0205</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5862000000000001</v>
+        <v>0.407</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1067</v>
+        <v>-2.8164</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2338</v>
+        <v>-1.7033</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1271</v>
+        <v>-1.1132</v>
       </c>
       <c r="P5" t="n">
         <v>0.386</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.158</v>
       </c>
       <c r="R5" t="n">
-        <v>0.386</v>
+        <v>1.5441</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8758</v>
+        <v>-0.4812</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3569</v>
+        <v>-0.3523</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5189</v>
+        <v>-0.1289</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.9421</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. CARTÓN CHARFOLE</t>
+          <t>I. VILLAVERDE GONZALEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.0103</v>
+        <v>-1.6941</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7502</v>
+        <v>0.1419</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2601</v>
+        <v>-1.8361</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3009</v>
+        <v>-1.0372</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8123</v>
+        <v>-0.9087</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1132</v>
+        <v>-0.1285</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3564</v>
+        <v>0.4176</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4035</v>
+        <v>-0.2743</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9529</v>
+        <v>0.6919</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0555</v>
+        <v>-1.4548</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2158</v>
+        <v>-0.6344</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8397</v>
+        <v>-0.8204</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.0881</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7371</v>
+        <v>0.579</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2883</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0185</v>
+        <v>-0.2756</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.2698</v>
+        <v>0.2677</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3281</v>
+        <v>-1.228</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3281</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. VILLAVERDE GONZALEZ</t>
+          <t>R. CARTÓN CHARFOLE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.055</v>
+        <v>-2.3058</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0583</v>
+        <v>-1.0724</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9967</v>
+        <v>-1.2334</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0372</v>
+        <v>0.3009</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9087</v>
+        <v>-0.8123</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1285</v>
+        <v>1.1132</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4176</v>
+        <v>2.3564</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2743</v>
+        <v>0.4035</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6919</v>
+        <v>1.9529</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4548</v>
+        <v>-2.0555</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6344</v>
+        <v>-1.2158</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8204</v>
+        <v>-0.8397</v>
       </c>
       <c r="P7" t="n">
-        <v>0.579</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.0881</v>
       </c>
       <c r="R7" t="n">
-        <v>0.579</v>
+        <v>1.7371</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3688</v>
+        <v>-1.5837</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4759</v>
+        <v>-0.3407</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1071</v>
+        <v>-1.243</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.228</v>
+        <v>0.3281</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.228</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.6495</v>
+        <v>-5.1627</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.7144</v>
+        <v>-5.4952</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0648</v>
+        <v>0.3325</v>
       </c>
       <c r="G8" t="n">
         <v>-3.9458</v>
@@ -1078,13 +1078,13 @@
         <v>1.158</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.1826</v>
+        <v>-1.6958</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2492</v>
+        <v>-1.0301</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9333</v>
+        <v>-0.6656</v>
       </c>
       <c r="V8" t="n">
         <v>0.2859</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.8164</v>
+        <v>-5.2969</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7894</v>
+        <v>-1.2699</v>
       </c>
       <c r="F9" t="n">
         <v>-4.0271</v>
@@ -1156,10 +1156,10 @@
         <v>1.3511</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.0927</v>
+        <v>-1.5732</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.4132</v>
+        <v>-0.8935999999999999</v>
       </c>
       <c r="U9" t="n">
         <v>-0.6795</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.5041</v>
+        <v>-7.3712</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.4056</v>
+        <v>-6.005</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0985</v>
+        <v>-1.3662</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5748</v>
@@ -1234,13 +1234,13 @@
         <v>1.3511</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0232</v>
+        <v>-0.8904</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2942</v>
+        <v>-0.8935999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.271</v>
+        <v>0.0033</v>
       </c>
       <c r="V10" t="n">
         <v>0.6562</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-23.3229</v>
+        <v>-22.4307</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.5434</v>
+        <v>-10.6512</v>
       </c>
       <c r="F11" t="n">
-        <v>-11.7797</v>
+        <v>-11.7798</v>
       </c>
       <c r="G11" t="n">
         <v>-6.749199999999999</v>
@@ -1312,13 +1312,13 @@
         <v>9.650400000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>-10.166</v>
+        <v>-9.2738</v>
       </c>
       <c r="T11" t="n">
-        <v>-6.1073</v>
+        <v>-5.2149</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.0586</v>
+        <v>-4.0585</v>
       </c>
       <c r="V11" t="n">
         <v>1.3124</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.3795</v>
+        <v>6.3061</v>
       </c>
       <c r="E12" t="n">
-        <v>4.7044</v>
+        <v>4.6042</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6751</v>
+        <v>1.7019</v>
       </c>
       <c r="G12" t="n">
         <v>4.6873</v>
@@ -1390,13 +1390,13 @@
         <v>1.7371</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.538</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1468</v>
+        <v>0.0466</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4647</v>
+        <v>0.4914</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6562</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. SAVITSKI SAVITSKAIA</t>
+          <t>M. ARIZTIMUÑO MORRAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.588</v>
+        <v>4.0795</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7948</v>
+        <v>3.4703</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7932</v>
+        <v>0.6092</v>
       </c>
       <c r="G13" t="n">
-        <v>2.438</v>
+        <v>1.2594</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4216</v>
+        <v>1.4758</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0164</v>
+        <v>-0.2164</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6305</v>
+        <v>1.8589</v>
       </c>
       <c r="K13" t="n">
-        <v>1.9143</v>
+        <v>1.1021</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.7569</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1925</v>
+        <v>-0.5995</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5072</v>
+        <v>0.3737</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6998</v>
+        <v>-0.9732</v>
       </c>
       <c r="P13" t="n">
-        <v>0.772</v>
+        <v>1.7371</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>1.7371</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3201</v>
+        <v>1.083</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8435</v>
+        <v>0.3834</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4766</v>
+        <v>0.6996</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9421</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2859</v>
+        <v>1.228</v>
       </c>
       <c r="X13" t="n">
         <v>-1.228</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K. ABU SHAMS SANCHEZ</t>
+          <t>A. SAVITSKI SAVITSKAIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.708</v>
+        <v>3.8788</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3947</v>
+        <v>2.5945</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3133</v>
+        <v>1.2842</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3458</v>
+        <v>2.438</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6807</v>
+        <v>2.4216</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.3348</v>
+        <v>0.0164</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8054</v>
+        <v>2.6305</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1734</v>
+        <v>1.9143</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.368</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4596</v>
+        <v>-0.1925</v>
       </c>
       <c r="N14" t="n">
         <v>0.5072</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9668</v>
+        <v>-0.6998</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5441</v>
+        <v>0.772</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5441</v>
+        <v>1.7371</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1462</v>
+        <v>1.6108</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6895</v>
+        <v>0.6432</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4567</v>
+        <v>0.9677</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3281</v>
+        <v>-0.9421</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8999</v>
+        <v>0.2859</v>
       </c>
       <c r="X14" t="n">
         <v>-1.228</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. ARIZTIMUÑO MORRAS</t>
+          <t>J. ZHANG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9575</v>
+        <v>2.9939</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6692</v>
+        <v>1.9419</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2883</v>
+        <v>1.0521</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2594</v>
+        <v>2.0587</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4758</v>
+        <v>-0.6603</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2164</v>
+        <v>2.719</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8589</v>
+        <v>3.3392</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1021</v>
+        <v>-0.4865</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7569</v>
+        <v>3.8257</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5995</v>
+        <v>-1.2805</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3737</v>
+        <v>-0.1738</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9732</v>
+        <v>-1.1067</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7371</v>
+        <v>0.965</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7371</v>
+        <v>1.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.039</v>
+        <v>-0.0297</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4177</v>
+        <v>-0.4323</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3787</v>
+        <v>0.4025</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. ZHANG</t>
+          <t>K. ABU SHAMS SANCHEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5398</v>
+        <v>2.853</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5413</v>
+        <v>2.5936</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.2594</v>
       </c>
       <c r="G16" t="n">
-        <v>2.0587</v>
+        <v>0.3458</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6603</v>
+        <v>2.6807</v>
       </c>
       <c r="I16" t="n">
-        <v>2.719</v>
+        <v>-2.3348</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3392</v>
+        <v>0.8054</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4865</v>
+        <v>2.1734</v>
       </c>
       <c r="L16" t="n">
-        <v>3.8257</v>
+        <v>-1.368</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2805</v>
+        <v>-0.4596</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1738</v>
+        <v>0.5072</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1067</v>
+        <v>-0.9668</v>
       </c>
       <c r="P16" t="n">
-        <v>0.965</v>
+        <v>1.5441</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9301</v>
+        <v>1.5441</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4838</v>
+        <v>1.2912</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8328</v>
+        <v>0.8884</v>
       </c>
       <c r="U16" t="n">
-        <v>0.349</v>
+        <v>0.4028</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.3281</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.8999</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4338</v>
+        <v>2.7541</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7186</v>
+        <v>1.1192</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7152</v>
+        <v>1.6349</v>
       </c>
       <c r="G17" t="n">
         <v>0.9869</v>
@@ -1780,13 +1780,13 @@
         <v>0.772</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.9951</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1943</v>
+        <v>0.2062</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8692</v>
+        <v>0.7889</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0575</v>
+        <v>2.6322</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2455</v>
+        <v>1.4457</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8120000000000001</v>
+        <v>1.1865</v>
       </c>
       <c r="G18" t="n">
         <v>1.1261</v>
@@ -1858,13 +1858,13 @@
         <v>1.9301</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0337</v>
+        <v>0.541</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1361</v>
+        <v>0.0641</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1024</v>
+        <v>0.4769</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GARCIA IBAÑEZ</t>
+          <t>H. OREJA ELSO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8799</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3803</v>
+        <v>-1.0526</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4996</v>
+        <v>1.7095</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4264</v>
+        <v>-0.1367</v>
       </c>
       <c r="H19" t="n">
-        <v>0.265</v>
+        <v>-0.2702</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1614</v>
+        <v>0.1335</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1856</v>
+        <v>0.4564</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1449</v>
+        <v>-0.2434</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0407</v>
+        <v>0.6998</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2408</v>
+        <v>-0.5931</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1201</v>
+        <v>-0.0268</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1207</v>
+        <v>-0.5662</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.158</v>
+        <v>-0.193</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>0.772</v>
+        <v>1.7371</v>
       </c>
       <c r="S19" t="n">
-        <v>2.2256</v>
+        <v>0.9865</v>
       </c>
       <c r="T19" t="n">
-        <v>1.8389</v>
+        <v>0.4211</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3867</v>
+        <v>0.5655</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. OREJA ELSO</t>
+          <t>A. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1085</v>
+        <v>0.0123</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2529</v>
+        <v>-0.6211</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3615</v>
+        <v>0.6335</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1367</v>
+        <v>0.4264</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2702</v>
+        <v>0.265</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1335</v>
+        <v>0.1614</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4564</v>
+        <v>0.1856</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2434</v>
+        <v>0.1449</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6998</v>
+        <v>0.0407</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5931</v>
+        <v>0.2408</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0268</v>
+        <v>0.1201</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5662</v>
+        <v>0.1207</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.193</v>
+        <v>-1.158</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7371</v>
+        <v>0.772</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4382</v>
+        <v>1.358</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2208</v>
+        <v>0.8375</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2175</v>
+        <v>0.5205</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.3538</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3642</v>
+        <v>-1.7634</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6773</v>
+        <v>1.4096</v>
       </c>
       <c r="G21" t="n">
         <v>-3.5677</v>
@@ -2092,13 +2092,13 @@
         <v>1.7371</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5949</v>
+        <v>0.928</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5658</v>
+        <v>0.0351</v>
       </c>
       <c r="U21" t="n">
-        <v>1.1607</v>
+        <v>0.893</v>
       </c>
       <c r="V21" t="n">
         <v>1.5138</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6426</v>
+        <v>-1.8224</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.052</v>
+        <v>-2.5528</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4095</v>
+        <v>0.7304</v>
       </c>
       <c r="G22" t="n">
         <v>-2.875</v>
@@ -2170,13 +2170,13 @@
         <v>1.7371</v>
       </c>
       <c r="S22" t="n">
-        <v>1.7113</v>
+        <v>1.5315</v>
       </c>
       <c r="T22" t="n">
-        <v>1.4661</v>
+        <v>0.9654</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2452</v>
+        <v>0.5661</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2859</v>
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>23.3229</v>
+        <v>23.9905</v>
       </c>
       <c r="E23" t="n">
-        <v>11.7797</v>
+        <v>11.7795</v>
       </c>
       <c r="F23" t="n">
-        <v>11.5435</v>
+        <v>12.2112</v>
       </c>
       <c r="G23" t="n">
-        <v>6.7492</v>
+        <v>6.749199999999998</v>
       </c>
       <c r="H23" t="n">
-        <v>7.513399999999998</v>
+        <v>7.5134</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7640000000000006</v>
+        <v>-0.7640000000000001</v>
       </c>
       <c r="J23" t="n">
         <v>13.8139</v>
@@ -2227,10 +2227,10 @@
         <v>6.881</v>
       </c>
       <c r="L23" t="n">
-        <v>6.933399999999999</v>
+        <v>6.9334</v>
       </c>
       <c r="M23" t="n">
-        <v>-7.065</v>
+        <v>-7.064999999999999</v>
       </c>
       <c r="N23" t="n">
         <v>0.6322999999999999</v>
@@ -2239,7 +2239,7 @@
         <v>-7.6972</v>
       </c>
       <c r="P23" t="n">
-        <v>7.720300000000002</v>
+        <v>7.7203</v>
       </c>
       <c r="Q23" t="n">
         <v>-9.6503</v>
@@ -2248,13 +2248,13 @@
         <v>17.3709</v>
       </c>
       <c r="S23" t="n">
-        <v>10.1661</v>
+        <v>10.8334</v>
       </c>
       <c r="T23" t="n">
-        <v>4.0589</v>
+        <v>4.0587</v>
       </c>
       <c r="U23" t="n">
-        <v>6.1074</v>
+        <v>6.774900000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3125</v>
